--- a/Result/profitability/4543.xlsx
+++ b/Result/profitability/4543.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7161,6 +7161,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>241</v>
+      </c>
+      <c r="D54" t="n">
+        <v>169</v>
+      </c>
+      <c r="E54" t="n">
+        <v>72</v>
+      </c>
+      <c r="F54" t="n">
+        <v>29.76</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>14.35%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>10</v>
+      </c>
+      <c r="J54" t="n">
+        <v>44</v>
+      </c>
+      <c r="K54" t="n">
+        <v>36</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="N54" t="n">
+        <v>26.395</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-0.1973684210526316</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-4.289999999999996</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-0.1259911894273127</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-1.635416666666667</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>0.5253716043054844</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
